--- a/youzi/zhouyu1933/index.xlsx
+++ b/youzi/zhouyu1933/index.xlsx
@@ -51,6 +51,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -159,30 +171,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -195,6 +183,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -219,55 +219,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1402,7 +1402,7 @@
       <c r="C2" t="str">
         <v>002796</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="5" t="str">
         <v>净卖: -1884.66万</v>
       </c>
       <c r="E2">
@@ -1417,40 +1417,40 @@
       <c r="H2">
         <v>-4.98</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="2">
         <v>15.8</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="8">
         <v>14.1</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="11">
         <v>19.74</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="6">
         <v>23.93</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="12">
         <v>36.33</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="3">
         <v>26.49</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="13">
         <v>39.15</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="7">
         <v>28.46</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="9">
         <v>26.03</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="4">
         <v>15.67</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="10">
         <v>21.25</v>
       </c>
-      <c r="T2" s="6">
+      <c r="T2" s="1">
         <v>249.84</v>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       <c r="C3" t="str">
         <v>300593</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="23" t="str">
         <v>净卖: -2424.73万</v>
       </c>
       <c r="E3">
@@ -1479,40 +1479,40 @@
       <c r="H3">
         <v>0.44</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="24">
         <v>19.48</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="25">
         <v>19.6</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="21">
         <v>18.53</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="18">
         <v>23.07</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="20">
         <v>16.24</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3" s="19">
         <v>17.58</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="26">
         <v>17.19</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="14">
         <v>22.72</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="15">
         <v>29.95</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="22">
         <v>35.72</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="16">
         <v>35.16</v>
       </c>
-      <c r="T3" s="18">
+      <c r="T3" s="17">
         <v>16.2</v>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       <c r="C4" t="str">
         <v>300448</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="39" t="str">
         <v>净卖: -2570.21万</v>
       </c>
       <c r="E4">
@@ -1541,13 +1541,13 @@
       <c r="H4">
         <v>-0.83</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="27">
         <v>-14.81</v>
       </c>
       <c r="J4" s="35">
         <v>-20.46</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="31">
         <v>-16.67</v>
       </c>
       <c r="L4" s="36">
@@ -1556,10 +1556,10 @@
       <c r="M4" s="37">
         <v>-21.85</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="38">
         <v>-24.26</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="28">
         <v>-27.78</v>
       </c>
       <c r="P4" s="29">
@@ -1568,13 +1568,13 @@
       <c r="Q4" s="32">
         <v>-29.72</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="33">
         <v>-31.11</v>
       </c>
-      <c r="S4" s="33">
+      <c r="S4" s="34">
         <v>-34.81</v>
       </c>
-      <c r="T4" s="28">
+      <c r="T4" s="30">
         <v>-37.78</v>
       </c>
     </row>
@@ -1637,40 +1637,40 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="43">
+      <c r="I6" s="40">
         <v>66.67</v>
       </c>
-      <c r="J6" s="47">
+      <c r="J6" s="41">
         <v>66.67</v>
       </c>
-      <c r="K6" s="48">
+      <c r="K6" s="46">
         <v>66.67</v>
       </c>
-      <c r="L6" s="44">
+      <c r="L6" s="42">
         <v>66.67</v>
       </c>
-      <c r="M6" s="40">
+      <c r="M6" s="43">
         <v>66.67</v>
       </c>
-      <c r="N6" s="49">
+      <c r="N6" s="44">
         <v>66.67</v>
       </c>
-      <c r="O6" s="41">
+      <c r="O6" s="49">
         <v>66.67</v>
       </c>
-      <c r="P6" s="50">
+      <c r="P6" s="45">
         <v>66.67</v>
       </c>
-      <c r="Q6" s="42">
+      <c r="Q6" s="50">
         <v>66.67</v>
       </c>
       <c r="R6" s="51">
         <v>66.67</v>
       </c>
-      <c r="S6" s="45">
+      <c r="S6" s="47">
         <v>66.67</v>
       </c>
-      <c r="T6" s="46">
+      <c r="T6" s="48">
         <v>66.67</v>
       </c>
     </row>
@@ -1685,37 +1685,37 @@
       <c r="F7" t="str"/>
       <c r="G7" t="str"/>
       <c r="H7" t="str"/>
-      <c r="I7" s="56">
+      <c r="I7" s="58">
         <v>6.82</v>
       </c>
-      <c r="J7" s="57">
+      <c r="J7" s="56">
         <v>4.41</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7" s="59">
         <v>7.2</v>
       </c>
-      <c r="L7" s="58">
+      <c r="L7" s="60">
         <v>7.92</v>
       </c>
-      <c r="M7" s="63">
+      <c r="M7" s="53">
         <v>10.24</v>
       </c>
-      <c r="N7" s="60">
+      <c r="N7" s="61">
         <v>6.6</v>
       </c>
-      <c r="O7" s="59">
+      <c r="O7" s="57">
         <v>9.52</v>
       </c>
-      <c r="P7" s="61">
+      <c r="P7" s="62">
         <v>6.23</v>
       </c>
-      <c r="Q7" s="53">
+      <c r="Q7" s="63">
         <v>8.75</v>
       </c>
-      <c r="R7" s="54">
+      <c r="R7" s="52">
         <v>6.76</v>
       </c>
-      <c r="S7" s="62">
+      <c r="S7" s="54">
         <v>7.2</v>
       </c>
       <c r="T7" s="55">

--- a/youzi/zhouyu1933/index.xlsx
+++ b/youzi/zhouyu1933/index.xlsx
@@ -63,6 +63,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -99,78 +141,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -195,6 +165,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -213,6 +213,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -262,12 +268,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1402,7 +1402,7 @@
       <c r="C2" t="str">
         <v>002796</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="12" t="str">
         <v>净卖: -1884.66万</v>
       </c>
       <c r="E2">
@@ -1417,40 +1417,40 @@
       <c r="H2">
         <v>-4.98</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="5">
         <v>15.8</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="13">
         <v>14.1</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="3">
         <v>19.74</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="10">
         <v>23.93</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="4">
         <v>36.33</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="6">
         <v>26.49</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="11">
         <v>39.15</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="1">
         <v>28.46</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="Q2" s="7">
         <v>26.03</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="8">
         <v>15.67</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="2">
         <v>21.25</v>
       </c>
-      <c r="T2" s="1">
+      <c r="T2" s="9">
         <v>249.84</v>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       <c r="C3" t="str">
         <v>300593</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="18" t="str">
         <v>净卖: -2424.73万</v>
       </c>
       <c r="E3">
@@ -1479,37 +1479,37 @@
       <c r="H3">
         <v>0.44</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="22">
         <v>19.48</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="23">
         <v>19.6</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="26">
         <v>18.53</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="14">
         <v>23.07</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="15">
         <v>16.24</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="24">
         <v>17.58</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="19">
         <v>17.19</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="25">
         <v>22.72</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="20">
         <v>29.95</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="16">
         <v>35.72</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="21">
         <v>35.16</v>
       </c>
       <c r="T3" s="17">
@@ -1526,7 +1526,7 @@
       <c r="C4" t="str">
         <v>300448</v>
       </c>
-      <c r="D4" s="39" t="str">
+      <c r="D4" s="30" t="str">
         <v>净卖: -2570.21万</v>
       </c>
       <c r="E4">
@@ -1541,40 +1541,40 @@
       <c r="H4">
         <v>-0.83</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="34">
         <v>-14.81</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="31">
         <v>-20.46</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="28">
         <v>-16.67</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="38">
         <v>-23.24</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="35">
         <v>-21.85</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="32">
         <v>-24.26</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="36">
         <v>-27.78</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="33">
         <v>-32.5</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="29">
         <v>-29.72</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="39">
         <v>-31.11</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="27">
         <v>-34.81</v>
       </c>
-      <c r="T4" s="30">
+      <c r="T4" s="37">
         <v>-37.78</v>
       </c>
     </row>
@@ -1637,40 +1637,40 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="40">
+      <c r="I6" s="47">
         <v>66.67</v>
       </c>
-      <c r="J6" s="41">
+      <c r="J6" s="46">
         <v>66.67</v>
       </c>
-      <c r="K6" s="46">
+      <c r="K6" s="48">
         <v>66.67</v>
       </c>
       <c r="L6" s="42">
         <v>66.67</v>
       </c>
-      <c r="M6" s="43">
+      <c r="M6" s="50">
         <v>66.67</v>
       </c>
-      <c r="N6" s="44">
+      <c r="N6" s="49">
         <v>66.67</v>
       </c>
-      <c r="O6" s="49">
+      <c r="O6" s="51">
         <v>66.67</v>
       </c>
-      <c r="P6" s="45">
+      <c r="P6" s="43">
         <v>66.67</v>
       </c>
-      <c r="Q6" s="50">
+      <c r="Q6" s="44">
         <v>66.67</v>
       </c>
-      <c r="R6" s="51">
+      <c r="R6" s="40">
         <v>66.67</v>
       </c>
-      <c r="S6" s="47">
+      <c r="S6" s="41">
         <v>66.67</v>
       </c>
-      <c r="T6" s="48">
+      <c r="T6" s="45">
         <v>66.67</v>
       </c>
     </row>
@@ -1685,40 +1685,40 @@
       <c r="F7" t="str"/>
       <c r="G7" t="str"/>
       <c r="H7" t="str"/>
-      <c r="I7" s="58">
+      <c r="I7" s="59">
         <v>6.82</v>
       </c>
-      <c r="J7" s="56">
+      <c r="J7" s="60">
         <v>4.41</v>
       </c>
-      <c r="K7" s="59">
+      <c r="K7" s="61">
         <v>7.2</v>
       </c>
-      <c r="L7" s="60">
+      <c r="L7" s="52">
         <v>7.92</v>
       </c>
-      <c r="M7" s="53">
+      <c r="M7" s="57">
         <v>10.24</v>
       </c>
-      <c r="N7" s="61">
+      <c r="N7" s="53">
         <v>6.6</v>
       </c>
-      <c r="O7" s="57">
+      <c r="O7" s="58">
         <v>9.52</v>
       </c>
-      <c r="P7" s="62">
+      <c r="P7" s="54">
         <v>6.23</v>
       </c>
-      <c r="Q7" s="63">
+      <c r="Q7" s="62">
         <v>8.75</v>
       </c>
-      <c r="R7" s="52">
+      <c r="R7" s="55">
         <v>6.76</v>
       </c>
-      <c r="S7" s="54">
+      <c r="S7" s="56">
         <v>7.2</v>
       </c>
-      <c r="T7" s="55">
+      <c r="T7" s="63">
         <v>76.09</v>
       </c>
     </row>

--- a/youzi/zhouyu1933/index.xlsx
+++ b/youzi/zhouyu1933/index.xlsx
@@ -117,30 +117,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -195,6 +171,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -207,13 +207,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1417,41 +1417,41 @@
       <c r="H2">
         <v>-4.98</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="3">
         <v>15.8</v>
       </c>
       <c r="J2" s="13">
         <v>14.1</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="8">
         <v>19.74</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="5">
         <v>23.93</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="9">
         <v>36.33</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="10">
         <v>26.49</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="6">
         <v>39.15</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="11">
         <v>28.46</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="1">
         <v>26.03</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="4">
         <v>15.67</v>
       </c>
       <c r="S2" s="2">
         <v>21.25</v>
       </c>
-      <c r="T2" s="9">
-        <v>249.84</v>
+      <c r="T2" s="7">
+        <v>265.9</v>
       </c>
     </row>
     <row r="3">
@@ -1464,7 +1464,7 @@
       <c r="C3" t="str">
         <v>300593</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="14" t="str">
         <v>净卖: -2424.73万</v>
       </c>
       <c r="E3">
@@ -1482,38 +1482,38 @@
       <c r="I3" s="22">
         <v>19.48</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="15">
         <v>19.6</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="16">
         <v>18.53</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="23">
         <v>23.07</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="17">
         <v>16.24</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="18">
         <v>17.58</v>
       </c>
       <c r="O3" s="19">
         <v>17.19</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="24">
         <v>22.72</v>
       </c>
       <c r="Q3" s="20">
         <v>29.95</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="21">
         <v>35.72</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="25">
         <v>35.16</v>
       </c>
-      <c r="T3" s="17">
-        <v>16.2</v>
+      <c r="T3" s="26">
+        <v>17.27</v>
       </c>
     </row>
     <row r="4">
@@ -1526,7 +1526,7 @@
       <c r="C4" t="str">
         <v>300448</v>
       </c>
-      <c r="D4" s="30" t="str">
+      <c r="D4" s="29" t="str">
         <v>净卖: -2570.21万</v>
       </c>
       <c r="E4">
@@ -1541,41 +1541,41 @@
       <c r="H4">
         <v>-0.83</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="32">
         <v>-14.81</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="34">
         <v>-20.46</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="33">
         <v>-16.67</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="30">
         <v>-23.24</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="31">
         <v>-21.85</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="27">
         <v>-24.26</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="35">
         <v>-27.78</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="28">
         <v>-32.5</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="36">
         <v>-29.72</v>
       </c>
-      <c r="R4" s="39">
+      <c r="R4" s="37">
         <v>-31.11</v>
       </c>
-      <c r="S4" s="27">
+      <c r="S4" s="38">
         <v>-34.81</v>
       </c>
-      <c r="T4" s="37">
-        <v>-37.78</v>
+      <c r="T4" s="39">
+        <v>-35.46</v>
       </c>
     </row>
     <row r="5">
@@ -1637,13 +1637,13 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="47">
+      <c r="I6" s="44">
         <v>66.67</v>
       </c>
-      <c r="J6" s="46">
+      <c r="J6" s="40">
         <v>66.67</v>
       </c>
-      <c r="K6" s="48">
+      <c r="K6" s="41">
         <v>66.67</v>
       </c>
       <c r="L6" s="42">
@@ -1652,25 +1652,25 @@
       <c r="M6" s="50">
         <v>66.67</v>
       </c>
-      <c r="N6" s="49">
+      <c r="N6" s="43">
         <v>66.67</v>
       </c>
-      <c r="O6" s="51">
+      <c r="O6" s="45">
         <v>66.67</v>
       </c>
-      <c r="P6" s="43">
+      <c r="P6" s="48">
         <v>66.67</v>
       </c>
-      <c r="Q6" s="44">
+      <c r="Q6" s="51">
         <v>66.67</v>
       </c>
-      <c r="R6" s="40">
+      <c r="R6" s="46">
         <v>66.67</v>
       </c>
-      <c r="S6" s="41">
+      <c r="S6" s="49">
         <v>66.67</v>
       </c>
-      <c r="T6" s="45">
+      <c r="T6" s="47">
         <v>66.67</v>
       </c>
     </row>
@@ -1685,41 +1685,41 @@
       <c r="F7" t="str"/>
       <c r="G7" t="str"/>
       <c r="H7" t="str"/>
-      <c r="I7" s="59">
+      <c r="I7" s="52">
         <v>6.82</v>
       </c>
       <c r="J7" s="60">
         <v>4.41</v>
       </c>
-      <c r="K7" s="61">
+      <c r="K7" s="57">
         <v>7.2</v>
       </c>
-      <c r="L7" s="52">
+      <c r="L7" s="61">
         <v>7.92</v>
       </c>
-      <c r="M7" s="57">
+      <c r="M7" s="62">
         <v>10.24</v>
       </c>
-      <c r="N7" s="53">
+      <c r="N7" s="58">
         <v>6.6</v>
       </c>
-      <c r="O7" s="58">
+      <c r="O7" s="53">
         <v>9.52</v>
       </c>
       <c r="P7" s="54">
         <v>6.23</v>
       </c>
-      <c r="Q7" s="62">
+      <c r="Q7" s="55">
         <v>8.75</v>
       </c>
-      <c r="R7" s="55">
+      <c r="R7" s="56">
         <v>6.76</v>
       </c>
-      <c r="S7" s="56">
+      <c r="S7" s="63">
         <v>7.2</v>
       </c>
-      <c r="T7" s="63">
-        <v>76.09</v>
+      <c r="T7" s="59">
+        <v>82.57</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/zhouyu1933/index.xlsx
+++ b/youzi/zhouyu1933/index.xlsx
@@ -69,42 +69,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -117,6 +81,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -207,49 +207,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1402,7 +1402,7 @@
       <c r="C2" t="str">
         <v>002796</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="6" t="str">
         <v>净卖: -1884.66万</v>
       </c>
       <c r="E2">
@@ -1417,41 +1417,41 @@
       <c r="H2">
         <v>-4.98</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="10">
         <v>15.8</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="11">
         <v>14.1</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="7">
         <v>19.74</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="12">
         <v>23.93</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="13">
         <v>36.33</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="8">
         <v>26.49</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="9">
         <v>39.15</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="1">
         <v>28.46</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>26.03</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="5">
         <v>15.67</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="3">
         <v>21.25</v>
       </c>
-      <c r="T2" s="7">
-        <v>265.9</v>
+      <c r="T2" s="4">
+        <v>265.97</v>
       </c>
     </row>
     <row r="3">
@@ -1479,41 +1479,41 @@
       <c r="H3">
         <v>0.44</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="18">
         <v>19.48</v>
       </c>
       <c r="J3" s="15">
         <v>19.6</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="19">
         <v>18.53</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="16">
         <v>23.07</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="23">
         <v>16.24</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="17">
         <v>17.58</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="24">
         <v>17.19</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="20">
         <v>22.72</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="21">
         <v>29.95</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="22">
         <v>35.72</v>
       </c>
       <c r="S3" s="25">
         <v>35.16</v>
       </c>
       <c r="T3" s="26">
-        <v>17.27</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="4">
@@ -1526,7 +1526,7 @@
       <c r="C4" t="str">
         <v>300448</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="36" t="str">
         <v>净卖: -2570.21万</v>
       </c>
       <c r="E4">
@@ -1541,41 +1541,41 @@
       <c r="H4">
         <v>-0.83</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="39">
         <v>-14.81</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="32">
         <v>-20.46</v>
       </c>
       <c r="K4" s="33">
         <v>-16.67</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="27">
         <v>-23.24</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="28">
         <v>-21.85</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="34">
         <v>-24.26</v>
       </c>
       <c r="O4" s="35">
         <v>-27.78</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="29">
         <v>-32.5</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="30">
         <v>-29.72</v>
       </c>
       <c r="R4" s="37">
         <v>-31.11</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="31">
         <v>-34.81</v>
       </c>
-      <c r="T4" s="39">
-        <v>-35.46</v>
+      <c r="T4" s="38">
+        <v>-32.41</v>
       </c>
     </row>
     <row r="5">
@@ -1637,40 +1637,40 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="44">
+      <c r="I6" s="49">
         <v>66.67</v>
       </c>
-      <c r="J6" s="40">
+      <c r="J6" s="42">
         <v>66.67</v>
       </c>
-      <c r="K6" s="41">
+      <c r="K6" s="43">
         <v>66.67</v>
       </c>
-      <c r="L6" s="42">
+      <c r="L6" s="47">
         <v>66.67</v>
       </c>
-      <c r="M6" s="50">
+      <c r="M6" s="44">
         <v>66.67</v>
       </c>
-      <c r="N6" s="43">
+      <c r="N6" s="50">
         <v>66.67</v>
       </c>
-      <c r="O6" s="45">
+      <c r="O6" s="40">
         <v>66.67</v>
       </c>
-      <c r="P6" s="48">
+      <c r="P6" s="45">
         <v>66.67</v>
       </c>
-      <c r="Q6" s="51">
+      <c r="Q6" s="48">
         <v>66.67</v>
       </c>
       <c r="R6" s="46">
         <v>66.67</v>
       </c>
-      <c r="S6" s="49">
+      <c r="S6" s="51">
         <v>66.67</v>
       </c>
-      <c r="T6" s="47">
+      <c r="T6" s="41">
         <v>66.67</v>
       </c>
     </row>
@@ -1685,41 +1685,41 @@
       <c r="F7" t="str"/>
       <c r="G7" t="str"/>
       <c r="H7" t="str"/>
-      <c r="I7" s="52">
+      <c r="I7" s="60">
         <v>6.82</v>
       </c>
-      <c r="J7" s="60">
+      <c r="J7" s="55">
         <v>4.41</v>
       </c>
-      <c r="K7" s="57">
+      <c r="K7" s="56">
         <v>7.2</v>
       </c>
-      <c r="L7" s="61">
+      <c r="L7" s="57">
         <v>7.92</v>
       </c>
-      <c r="M7" s="62">
+      <c r="M7" s="58">
         <v>10.24</v>
       </c>
-      <c r="N7" s="58">
+      <c r="N7" s="61">
         <v>6.6</v>
       </c>
-      <c r="O7" s="53">
+      <c r="O7" s="52">
         <v>9.52</v>
       </c>
-      <c r="P7" s="54">
+      <c r="P7" s="59">
         <v>6.23</v>
       </c>
-      <c r="Q7" s="55">
+      <c r="Q7" s="53">
         <v>8.75</v>
       </c>
-      <c r="R7" s="56">
+      <c r="R7" s="54">
         <v>6.76</v>
       </c>
-      <c r="S7" s="63">
+      <c r="S7" s="62">
         <v>7.2</v>
       </c>
-      <c r="T7" s="59">
-        <v>82.57</v>
+      <c r="T7" s="63">
+        <v>83.4</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/zhouyu1933/index.xlsx
+++ b/youzi/zhouyu1933/index.xlsx
@@ -57,18 +57,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -117,6 +105,66 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -147,54 +195,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -207,6 +207,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -244,12 +250,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1402,7 +1402,7 @@
       <c r="C2" t="str">
         <v>002796</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="4" t="str">
         <v>净卖: -1884.66万</v>
       </c>
       <c r="E2">
@@ -1417,41 +1417,41 @@
       <c r="H2">
         <v>-4.98</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="5">
         <v>15.8</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="8">
         <v>14.1</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="13">
         <v>19.74</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="10">
         <v>23.93</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="11">
         <v>36.33</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="1">
         <v>26.49</v>
       </c>
       <c r="O2" s="9">
         <v>39.15</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="12">
         <v>28.46</v>
       </c>
       <c r="Q2" s="2">
         <v>26.03</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="6">
         <v>15.67</v>
       </c>
       <c r="S2" s="3">
         <v>21.25</v>
       </c>
-      <c r="T2" s="4">
-        <v>265.97</v>
+      <c r="T2" s="7">
+        <v>278.69</v>
       </c>
     </row>
     <row r="3">
@@ -1464,7 +1464,7 @@
       <c r="C3" t="str">
         <v>300593</v>
       </c>
-      <c r="D3" s="14" t="str">
+      <c r="D3" s="22" t="str">
         <v>净卖: -2424.73万</v>
       </c>
       <c r="E3">
@@ -1479,41 +1479,41 @@
       <c r="H3">
         <v>0.44</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="23">
         <v>19.48</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="24">
         <v>19.6</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="14">
         <v>18.53</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="15">
         <v>23.07</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="16">
         <v>16.24</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="19">
         <v>17.58</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="20">
         <v>17.19</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="21">
         <v>22.72</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="25">
         <v>29.95</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="26">
         <v>35.72</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="17">
         <v>35.16</v>
       </c>
-      <c r="T3" s="26">
-        <v>16.63</v>
+      <c r="T3" s="18">
+        <v>16.55</v>
       </c>
     </row>
     <row r="4">
@@ -1526,7 +1526,7 @@
       <c r="C4" t="str">
         <v>300448</v>
       </c>
-      <c r="D4" s="36" t="str">
+      <c r="D4" s="29" t="str">
         <v>净卖: -2570.21万</v>
       </c>
       <c r="E4">
@@ -1541,41 +1541,41 @@
       <c r="H4">
         <v>-0.83</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="33">
         <v>-14.81</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="30">
         <v>-20.46</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="38">
         <v>-16.67</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="36">
         <v>-23.24</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="39">
         <v>-21.85</v>
       </c>
       <c r="N4" s="34">
         <v>-24.26</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="31">
         <v>-27.78</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="35">
         <v>-32.5</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="37">
         <v>-29.72</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="32">
         <v>-31.11</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="27">
         <v>-34.81</v>
       </c>
-      <c r="T4" s="38">
-        <v>-32.41</v>
+      <c r="T4" s="28">
+        <v>-28.52</v>
       </c>
     </row>
     <row r="5">
@@ -1637,40 +1637,40 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="49">
+      <c r="I6" s="41">
         <v>66.67</v>
       </c>
-      <c r="J6" s="42">
+      <c r="J6" s="45">
         <v>66.67</v>
       </c>
-      <c r="K6" s="43">
+      <c r="K6" s="51">
         <v>66.67</v>
       </c>
-      <c r="L6" s="47">
+      <c r="L6" s="49">
         <v>66.67</v>
       </c>
-      <c r="M6" s="44">
+      <c r="M6" s="50">
         <v>66.67</v>
       </c>
-      <c r="N6" s="50">
+      <c r="N6" s="42">
         <v>66.67</v>
       </c>
-      <c r="O6" s="40">
+      <c r="O6" s="43">
         <v>66.67</v>
       </c>
-      <c r="P6" s="45">
+      <c r="P6" s="46">
         <v>66.67</v>
       </c>
-      <c r="Q6" s="48">
+      <c r="Q6" s="40">
         <v>66.67</v>
       </c>
-      <c r="R6" s="46">
+      <c r="R6" s="44">
         <v>66.67</v>
       </c>
-      <c r="S6" s="51">
+      <c r="S6" s="47">
         <v>66.67</v>
       </c>
-      <c r="T6" s="41">
+      <c r="T6" s="48">
         <v>66.67</v>
       </c>
     </row>
@@ -1685,41 +1685,41 @@
       <c r="F7" t="str"/>
       <c r="G7" t="str"/>
       <c r="H7" t="str"/>
-      <c r="I7" s="60">
+      <c r="I7" s="58">
         <v>6.82</v>
       </c>
-      <c r="J7" s="55">
+      <c r="J7" s="60">
         <v>4.41</v>
       </c>
-      <c r="K7" s="56">
+      <c r="K7" s="63">
         <v>7.2</v>
       </c>
-      <c r="L7" s="57">
+      <c r="L7" s="52">
         <v>7.92</v>
       </c>
-      <c r="M7" s="58">
+      <c r="M7" s="61">
         <v>10.24</v>
       </c>
-      <c r="N7" s="61">
+      <c r="N7" s="53">
         <v>6.6</v>
       </c>
-      <c r="O7" s="52">
+      <c r="O7" s="57">
         <v>9.52</v>
       </c>
-      <c r="P7" s="59">
+      <c r="P7" s="54">
         <v>6.23</v>
       </c>
-      <c r="Q7" s="53">
+      <c r="Q7" s="55">
         <v>8.75</v>
       </c>
-      <c r="R7" s="54">
+      <c r="R7" s="59">
         <v>6.76</v>
       </c>
-      <c r="S7" s="62">
+      <c r="S7" s="56">
         <v>7.2</v>
       </c>
-      <c r="T7" s="63">
-        <v>83.4</v>
+      <c r="T7" s="62">
+        <v>88.91</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/zhouyu1933/index.xlsx
+++ b/youzi/zhouyu1933/index.xlsx
@@ -45,18 +45,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -165,6 +153,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -189,25 +195,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1402,7 +1402,7 @@
       <c r="C2" t="str">
         <v>002796</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="2" t="str">
         <v>净卖: -1884.66万</v>
       </c>
       <c r="E2">
@@ -1417,41 +1417,41 @@
       <c r="H2">
         <v>-4.98</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="6">
         <v>15.8</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="7">
         <v>14.1</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="8">
         <v>19.74</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="13">
         <v>23.93</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="9">
         <v>36.33</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="3">
         <v>26.49</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="10">
         <v>39.15</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="11">
         <v>28.46</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="4">
         <v>26.03</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="12">
         <v>15.67</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="1">
         <v>21.25</v>
       </c>
-      <c r="T2" s="7">
-        <v>278.69</v>
+      <c r="T2" s="5">
+        <v>275.48</v>
       </c>
     </row>
     <row r="3">
@@ -1464,7 +1464,7 @@
       <c r="C3" t="str">
         <v>300593</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="23" t="str">
         <v>净卖: -2424.73万</v>
       </c>
       <c r="E3">
@@ -1479,41 +1479,41 @@
       <c r="H3">
         <v>0.44</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="24">
         <v>19.48</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="25">
         <v>19.6</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="19">
         <v>18.53</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="20">
         <v>23.07</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="15">
         <v>16.24</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="16">
         <v>17.58</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="21">
         <v>17.19</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="17">
         <v>22.72</v>
       </c>
-      <c r="Q3" s="25">
+      <c r="Q3" s="26">
         <v>29.95</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="14">
         <v>35.72</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="22">
         <v>35.16</v>
       </c>
       <c r="T3" s="18">
-        <v>16.55</v>
+        <v>18.77</v>
       </c>
     </row>
     <row r="4">
@@ -1526,7 +1526,7 @@
       <c r="C4" t="str">
         <v>300448</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="28" t="str">
         <v>净卖: -2570.21万</v>
       </c>
       <c r="E4">
@@ -1541,41 +1541,41 @@
       <c r="H4">
         <v>-0.83</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="29">
         <v>-14.81</v>
       </c>
       <c r="J4" s="30">
         <v>-20.46</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="31">
         <v>-16.67</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="32">
         <v>-23.24</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="33">
         <v>-21.85</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="35">
         <v>-24.26</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="34">
         <v>-27.78</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="39">
         <v>-32.5</v>
       </c>
-      <c r="Q4" s="37">
+      <c r="Q4" s="36">
         <v>-29.72</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="37">
         <v>-31.11</v>
       </c>
       <c r="S4" s="27">
         <v>-34.81</v>
       </c>
-      <c r="T4" s="28">
-        <v>-28.52</v>
+      <c r="T4" s="38">
+        <v>-28.06</v>
       </c>
     </row>
     <row r="5">
@@ -1637,40 +1637,40 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="41">
+      <c r="I6" s="44">
         <v>66.67</v>
       </c>
       <c r="J6" s="45">
         <v>66.67</v>
       </c>
-      <c r="K6" s="51">
+      <c r="K6" s="41">
         <v>66.67</v>
       </c>
-      <c r="L6" s="49">
+      <c r="L6" s="48">
         <v>66.67</v>
       </c>
-      <c r="M6" s="50">
+      <c r="M6" s="46">
         <v>66.67</v>
       </c>
       <c r="N6" s="42">
         <v>66.67</v>
       </c>
-      <c r="O6" s="43">
+      <c r="O6" s="49">
         <v>66.67</v>
       </c>
-      <c r="P6" s="46">
+      <c r="P6" s="50">
         <v>66.67</v>
       </c>
-      <c r="Q6" s="40">
+      <c r="Q6" s="51">
         <v>66.67</v>
       </c>
-      <c r="R6" s="44">
+      <c r="R6" s="40">
         <v>66.67</v>
       </c>
-      <c r="S6" s="47">
+      <c r="S6" s="43">
         <v>66.67</v>
       </c>
-      <c r="T6" s="48">
+      <c r="T6" s="47">
         <v>66.67</v>
       </c>
     </row>
@@ -1685,41 +1685,41 @@
       <c r="F7" t="str"/>
       <c r="G7" t="str"/>
       <c r="H7" t="str"/>
-      <c r="I7" s="58">
+      <c r="I7" s="54">
         <v>6.82</v>
       </c>
-      <c r="J7" s="60">
+      <c r="J7" s="55">
         <v>4.41</v>
       </c>
-      <c r="K7" s="63">
+      <c r="K7" s="52">
         <v>7.2</v>
       </c>
-      <c r="L7" s="52">
+      <c r="L7" s="60">
         <v>7.92</v>
       </c>
-      <c r="M7" s="61">
+      <c r="M7" s="57">
         <v>10.24</v>
       </c>
-      <c r="N7" s="53">
+      <c r="N7" s="56">
         <v>6.6</v>
       </c>
-      <c r="O7" s="57">
+      <c r="O7" s="53">
         <v>9.52</v>
       </c>
-      <c r="P7" s="54">
+      <c r="P7" s="61">
         <v>6.23</v>
       </c>
-      <c r="Q7" s="55">
+      <c r="Q7" s="58">
         <v>8.75</v>
       </c>
       <c r="R7" s="59">
         <v>6.76</v>
       </c>
-      <c r="S7" s="56">
+      <c r="S7" s="62">
         <v>7.2</v>
       </c>
-      <c r="T7" s="62">
-        <v>88.91</v>
+      <c r="T7" s="63">
+        <v>88.73</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/zhouyu1933/index.xlsx
+++ b/youzi/zhouyu1933/index.xlsx
@@ -45,6 +45,66 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -81,96 +141,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -195,43 +165,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1402,7 +1402,7 @@
       <c r="C2" t="str">
         <v>002796</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="12" t="str">
         <v>净卖: -1884.66万</v>
       </c>
       <c r="E2">
@@ -1417,41 +1417,41 @@
       <c r="H2">
         <v>-4.98</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="9">
         <v>15.8</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="6">
         <v>14.1</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="10">
         <v>19.74</v>
       </c>
       <c r="L2" s="13">
         <v>23.93</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="7">
         <v>36.33</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="1">
         <v>26.49</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="5">
         <v>39.15</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="2">
         <v>28.46</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="8">
         <v>26.03</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="3">
         <v>15.67</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="4">
         <v>21.25</v>
       </c>
-      <c r="T2" s="5">
-        <v>275.48</v>
+      <c r="T2" s="11">
+        <v>252.85</v>
       </c>
     </row>
     <row r="3">
@@ -1464,7 +1464,7 @@
       <c r="C3" t="str">
         <v>300593</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="18" t="str">
         <v>净卖: -2424.73万</v>
       </c>
       <c r="E3">
@@ -1479,41 +1479,41 @@
       <c r="H3">
         <v>0.44</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="19">
         <v>19.48</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="26">
         <v>19.6</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="20">
         <v>18.53</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="24">
         <v>23.07</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="16">
         <v>16.24</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="14">
         <v>17.58</v>
       </c>
       <c r="O3" s="21">
         <v>17.19</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="22">
         <v>22.72</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="23">
         <v>29.95</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="15">
         <v>35.72</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="25">
         <v>35.16</v>
       </c>
-      <c r="T3" s="18">
-        <v>18.77</v>
+      <c r="T3" s="17">
+        <v>13.35</v>
       </c>
     </row>
     <row r="4">
@@ -1526,7 +1526,7 @@
       <c r="C4" t="str">
         <v>300448</v>
       </c>
-      <c r="D4" s="28" t="str">
+      <c r="D4" s="33" t="str">
         <v>净卖: -2570.21万</v>
       </c>
       <c r="E4">
@@ -1541,41 +1541,41 @@
       <c r="H4">
         <v>-0.83</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="34">
         <v>-14.81</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="35">
         <v>-20.46</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="27">
         <v>-16.67</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="28">
         <v>-23.24</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="30">
         <v>-21.85</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="31">
         <v>-24.26</v>
       </c>
-      <c r="O4" s="34">
+      <c r="O4" s="36">
         <v>-27.78</v>
       </c>
-      <c r="P4" s="39">
+      <c r="P4" s="37">
         <v>-32.5</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="29">
         <v>-29.72</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="38">
         <v>-31.11</v>
       </c>
-      <c r="S4" s="27">
+      <c r="S4" s="39">
         <v>-34.81</v>
       </c>
-      <c r="T4" s="38">
-        <v>-28.06</v>
+      <c r="T4" s="32">
+        <v>-29.91</v>
       </c>
     </row>
     <row r="5">
@@ -1637,25 +1637,25 @@
       <c r="F6" t="str"/>
       <c r="G6" t="str"/>
       <c r="H6" t="str"/>
-      <c r="I6" s="44">
+      <c r="I6" s="41">
         <v>66.67</v>
       </c>
-      <c r="J6" s="45">
+      <c r="J6" s="44">
         <v>66.67</v>
       </c>
-      <c r="K6" s="41">
+      <c r="K6" s="45">
         <v>66.67</v>
       </c>
-      <c r="L6" s="48">
+      <c r="L6" s="42">
         <v>66.67</v>
       </c>
-      <c r="M6" s="46">
+      <c r="M6" s="49">
         <v>66.67</v>
       </c>
-      <c r="N6" s="42">
+      <c r="N6" s="46">
         <v>66.67</v>
       </c>
-      <c r="O6" s="49">
+      <c r="O6" s="47">
         <v>66.67</v>
       </c>
       <c r="P6" s="50">
@@ -1667,10 +1667,10 @@
       <c r="R6" s="40">
         <v>66.67</v>
       </c>
-      <c r="S6" s="43">
+      <c r="S6" s="48">
         <v>66.67</v>
       </c>
-      <c r="T6" s="47">
+      <c r="T6" s="43">
         <v>66.67</v>
       </c>
     </row>
@@ -1685,41 +1685,41 @@
       <c r="F7" t="str"/>
       <c r="G7" t="str"/>
       <c r="H7" t="str"/>
-      <c r="I7" s="54">
+      <c r="I7" s="57">
         <v>6.82</v>
       </c>
-      <c r="J7" s="55">
+      <c r="J7" s="53">
         <v>4.41</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7" s="61">
         <v>7.2</v>
       </c>
-      <c r="L7" s="60">
+      <c r="L7" s="54">
         <v>7.92</v>
       </c>
-      <c r="M7" s="57">
+      <c r="M7" s="58">
         <v>10.24</v>
       </c>
-      <c r="N7" s="56">
+      <c r="N7" s="62">
         <v>6.6</v>
       </c>
-      <c r="O7" s="53">
+      <c r="O7" s="59">
         <v>9.52</v>
       </c>
-      <c r="P7" s="61">
+      <c r="P7" s="60">
         <v>6.23</v>
       </c>
-      <c r="Q7" s="58">
+      <c r="Q7" s="63">
         <v>8.75</v>
       </c>
-      <c r="R7" s="59">
+      <c r="R7" s="52">
         <v>6.76</v>
       </c>
-      <c r="S7" s="62">
+      <c r="S7" s="55">
         <v>7.2</v>
       </c>
-      <c r="T7" s="63">
-        <v>88.73</v>
+      <c r="T7" s="56">
+        <v>78.76</v>
       </c>
     </row>
   </sheetData>
